--- a/output_boron/boron_Intermediate_hoenisch_2009.xlsx
+++ b/output_boron/boron_Intermediate_hoenisch_2009.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="317">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="333">
   <si>
     <t>NA</t>
   </si>
@@ -1370,7 +1370,7 @@
     <t xml:space="preserve">10.1126/science.1171477</t>
   </si>
   <si>
-    <t xml:space="preserve">https://www.ncei.noaa.gov/pub/data/paleo/climate_forcing/trace_gases/Paleo-pCO2/boron_isotopes_hoenisch_2009.xlsx</t>
+    <t xml:space="preserve">boron_isotopes_hoenisch_2009_p1.0.xlsx</t>
   </si>
   <si>
     <t xml:space="preserve">Harper and Giulivi</t>
@@ -1406,63 +1406,108 @@
     <t xml:space="preserve">ODP 668_B_1_1_25_27</t>
   </si>
   <si>
-    <t xml:space="preserve">Data updated from Hönisch &amp; Hemming 2005. The originally published d11B data were corrected by an instrument offset of +1.1‰ to match data collected on the 6" radius of curvature mass spectrometer at SUNY Stony Brook. Because that mass spectrometer is no longer in operation and because ongoing data collection is done on the Triton TIMS at LDEO, Stony Brook d11B data are now all adjusted to the Triton TIMS at LDEO, and data collected at LDEO are listed as measured.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">procedural 2009 duplicate, not included for data figures; Mg/Ca uncertainty: missing side filled using the archive's symmetric +/-3% specification.</t>
+    <t xml:space="preserve">Data updated from Hönisch &amp; Hemming 2005. The originally published d11B data were corrected by an instrument offset of +1.1‰ to match data collected on the 6" radius of curvature mass spectrometer at SUNY Stony Brook. Because that mass spectrometer is no longer in operation and because ongoing data collection is done on the Triton TIMS at LDEO, Stony Brook d11B data are now all adjusted to the Triton TIMS at LDEO, and data collected at LDEO are listed as measured.; Mg/Ca: 3.46, 3.56</t>
+  </si>
+  <si>
+    <t xml:space="preserve">procedural 2009 duplicate, not included for data figures; Mg/Ca: 3.46, 3.56; Mg/Ca error treated as symmetric using the stated +/-3%.</t>
   </si>
   <si>
     <t xml:space="preserve">ODP 668_B_1_1_33_35</t>
   </si>
   <si>
+    <t xml:space="preserve">Data updated from Hönisch &amp; Hemming 2005. The originally published d11B data were corrected by an instrument offset of +1.1‰ to match data collected on the 6" radius of curvature mass spectrometer at SUNY Stony Brook. Because that mass spectrometer is no longer in operation and because ongoing data collection is done on the Triton TIMS at LDEO, Stony Brook d11B data are now all adjusted to the Triton TIMS at LDEO, and data collected at LDEO are listed as measured.; Mg/Ca: 2.96, 2.81</t>
+  </si>
+  <si>
     <t xml:space="preserve">ODP 668_B_1_1_70_72</t>
   </si>
   <si>
+    <t xml:space="preserve">Data updated from Hönisch &amp; Hemming 2005. The originally published d11B data were corrected by an instrument offset of +1.1‰ to match data collected on the 6" radius of curvature mass spectrometer at SUNY Stony Brook. Because that mass spectrometer is no longer in operation and because ongoing data collection is done on the Triton TIMS at LDEO, Stony Brook d11B data are now all adjusted to the Triton TIMS at LDEO, and data collected at LDEO are listed as measured.; Mg/Ca: 2.99, 3.04</t>
+  </si>
+  <si>
     <t xml:space="preserve">ODP 668_B_1_1_105_107</t>
   </si>
   <si>
+    <t xml:space="preserve">Data updated from Hönisch &amp; Hemming 2005. The originally published d11B data were corrected by an instrument offset of +1.1‰ to match data collected on the 6" radius of curvature mass spectrometer at SUNY Stony Brook. Because that mass spectrometer is no longer in operation and because ongoing data collection is done on the Triton TIMS at LDEO, Stony Brook d11B data are now all adjusted to the Triton TIMS at LDEO, and data collected at LDEO are listed as measured.; Mg/Ca: 2.87, N/A</t>
+  </si>
+  <si>
     <t xml:space="preserve">ODP 668_B_1_2_25_27</t>
   </si>
   <si>
+    <t xml:space="preserve">Data updated from Hönisch &amp; Hemming 2005. The originally published d11B data were corrected by an instrument offset of +1.1‰ to match data collected on the 6" radius of curvature mass spectrometer at SUNY Stony Brook. Because that mass spectrometer is no longer in operation and because ongoing data collection is done on the Triton TIMS at LDEO, Stony Brook d11B data are now all adjusted to the Triton TIMS at LDEO, and data collected at LDEO are listed as measured.; Mg/Ca: 3.41, 3.41</t>
+  </si>
+  <si>
     <t xml:space="preserve">ODP 668_B_1_2_39_41</t>
   </si>
   <si>
+    <t xml:space="preserve">Data updated from Hönisch &amp; Hemming 2005. The originally published d11B data were corrected by an instrument offset of +1.1‰ to match data collected on the 6" radius of curvature mass spectrometer at SUNY Stony Brook. Because that mass spectrometer is no longer in operation and because ongoing data collection is done on the Triton TIMS at LDEO, Stony Brook d11B data are now all adjusted to the Triton TIMS at LDEO, and data collected at LDEO are listed as measured.; Mg/Ca: 4.04, 3.97</t>
+  </si>
+  <si>
     <t xml:space="preserve">ODP 668_B_1_2_49_51</t>
   </si>
   <si>
+    <t xml:space="preserve">Data updated from Hönisch &amp; Hemming 2005. The originally published d11B data were corrected by an instrument offset of +1.1‰ to match data collected on the 6" radius of curvature mass spectrometer at SUNY Stony Brook. Because that mass spectrometer is no longer in operation and because ongoing data collection is done on the Triton TIMS at LDEO, Stony Brook d11B data are now all adjusted to the Triton TIMS at LDEO, and data collected at LDEO are listed as measured.; Mg/Ca: 3.62, 3.82</t>
+  </si>
+  <si>
     <t xml:space="preserve">ODP 668_B_1_2_70_72</t>
   </si>
   <si>
+    <t xml:space="preserve">Data updated from Hönisch &amp; Hemming 2005. The originally published d11B data were corrected by an instrument offset of +1.1‰ to match data collected on the 6" radius of curvature mass spectrometer at SUNY Stony Brook. Because that mass spectrometer is no longer in operation and because ongoing data collection is done on the Triton TIMS at LDEO, Stony Brook d11B data are now all adjusted to the Triton TIMS at LDEO, and data collected at LDEO are listed as measured.; Mg/Ca: 2.86, 2.83</t>
+  </si>
+  <si>
     <t xml:space="preserve">ODP 668_B_1_2_74_76</t>
   </si>
   <si>
+    <t xml:space="preserve">Data updated from Hönisch &amp; Hemming 2005. The originally published d11B data were corrected by an instrument offset of +1.1‰ to match data collected on the 6" radius of curvature mass spectrometer at SUNY Stony Brook. Because that mass spectrometer is no longer in operation and because ongoing data collection is done on the Triton TIMS at LDEO, Stony Brook d11B data are now all adjusted to the Triton TIMS at LDEO, and data collected at LDEO are listed as measured.; Mg/Ca: 2.98, 3.02</t>
+  </si>
+  <si>
     <t xml:space="preserve">ODP 668_B_2_2_56_58</t>
   </si>
   <si>
+    <t xml:space="preserve">Data updated from Hönisch &amp; Hemming 2005. The originally published d11B data were corrected by an instrument offset of +1.1‰ to match data collected on the 6" radius of curvature mass spectrometer at SUNY Stony Brook. Because that mass spectrometer is no longer in operation and because ongoing data collection is done on the Triton TIMS at LDEO, Stony Brook d11B data are now all adjusted to the Triton TIMS at LDEO, and data collected at LDEO are listed as measured.; Mg/Ca: 3.20, 3.26</t>
+  </si>
+  <si>
     <t xml:space="preserve">ODP 668_B_2_2_105_107</t>
   </si>
   <si>
+    <t xml:space="preserve">Data updated from Hönisch &amp; Hemming 2005. The originally published d11B data were corrected by an instrument offset of +1.1‰ to match data collected on the 6" radius of curvature mass spectrometer at SUNY Stony Brook. Because that mass spectrometer is no longer in operation and because ongoing data collection is done on the Triton TIMS at LDEO, Stony Brook d11B data are now all adjusted to the Triton TIMS at LDEO, and data collected at LDEO are listed as measured.; Mg/Ca: 2.72, 2.88</t>
+  </si>
+  <si>
     <t xml:space="preserve">ODP 668_B_2_2_130_132</t>
   </si>
   <si>
+    <t xml:space="preserve">Data updated from Hönisch &amp; Hemming 2005. The originally published d11B data were corrected by an instrument offset of +1.1‰ to match data collected on the 6" radius of curvature mass spectrometer at SUNY Stony Brook. Because that mass spectrometer is no longer in operation and because ongoing data collection is done on the Triton TIMS at LDEO, Stony Brook d11B data are now all adjusted to the Triton TIMS at LDEO, and data collected at LDEO are listed as measured.; Mg/Ca: 2.88, 3.11</t>
+  </si>
+  <si>
     <t xml:space="preserve">ODP 668_B_2_3_14_16</t>
   </si>
   <si>
+    <t xml:space="preserve">Data updated from Hönisch &amp; Hemming 2005. The originally published d11B data were corrected by an instrument offset of +1.1‰ to match data collected on the 6" radius of curvature mass spectrometer at SUNY Stony Brook. Because that mass spectrometer is no longer in operation and because ongoing data collection is done on the Triton TIMS at LDEO, Stony Brook d11B data are now all adjusted to the Triton TIMS at LDEO, and data collected at LDEO are listed as measured.; Mg/Ca: 3.10, 3.28</t>
+  </si>
+  <si>
     <t xml:space="preserve">ODP 668_B_2_3_56_58</t>
   </si>
   <si>
+    <t xml:space="preserve">Data updated from Hönisch &amp; Hemming 2005. The originally published d11B data were corrected by an instrument offset of +1.1‰ to match data collected on the 6" radius of curvature mass spectrometer at SUNY Stony Brook. Because that mass spectrometer is no longer in operation and because ongoing data collection is done on the Triton TIMS at LDEO, Stony Brook d11B data are now all adjusted to the Triton TIMS at LDEO, and data collected at LDEO are listed as measured.; Mg/Ca: 3.61, 3.70</t>
+  </si>
+  <si>
     <t xml:space="preserve">ODP 668_B_2_3_70_72</t>
   </si>
   <si>
+    <t xml:space="preserve">Data updated from Hönisch &amp; Hemming 2005. The originally published d11B data were corrected by an instrument offset of +1.1‰ to match data collected on the 6" radius of curvature mass spectrometer at SUNY Stony Brook. Because that mass spectrometer is no longer in operation and because ongoing data collection is done on the Triton TIMS at LDEO, Stony Brook d11B data are now all adjusted to the Triton TIMS at LDEO, and data collected at LDEO are listed as measured.; Mg/Ca: 3.48, 3.36</t>
+  </si>
+  <si>
     <t xml:space="preserve">ODP 668_B_2_4_94_96</t>
   </si>
   <si>
+    <t xml:space="preserve">The originally published d11B data were corrected by an instrument offset of +1.1‰ to match data collected on the 6" radius of curvature mass spectrometer at SUNY Stony Brook. Because that mass spectrometer is no longer in operation and because ongoing data collection is done on the Triton TIMS at LDEO, Stony Brook d11B data are now all adjusted to the Triton TIMS at LDEO, and data collected at LDEO are listed as measured.; Mg/Ca: 3.18, 3.09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ODP 668_B_2_5_37_39</t>
+  </si>
+  <si>
     <t xml:space="preserve">The originally published d11B data were corrected by an instrument offset of +1.1‰ to match data collected on the 6" radius of curvature mass spectrometer at SUNY Stony Brook. Because that mass spectrometer is no longer in operation and because ongoing data collection is done on the Triton TIMS at LDEO, Stony Brook d11B data are now all adjusted to the Triton TIMS at LDEO, and data collected at LDEO are listed as measured.</t>
   </si>
   <si>
-    <t xml:space="preserve">ODP 668_B_2_5_37_39</t>
-  </si>
-  <si>
     <t xml:space="preserve">ODP 668_B_2_5_73_75</t>
   </si>
   <si>
@@ -1530,6 +1575,9 @@
   </si>
   <si>
     <t xml:space="preserve">ODP 668_B_3_6_3_5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">better match with stable isotope stratigraphy of ODP site 677 and geomagnetic information, see Dyez et al. (2018)</t>
   </si>
   <si>
     <t xml:space="preserve">ODP 668_B_3_6_80_82</t>
@@ -1600,7 +1648,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="9">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1660,12 +1708,6 @@
       <name val="Arial"/>
       <family val="2"/>
       <b/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <u val="single"/>
     </font>
   </fonts>
   <fills count="10">
@@ -1779,7 +1821,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1861,7 +1903,6 @@
     <xf numFmtId="0" fontId="8" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2468,7 +2509,7 @@
       <c r="B5" t="s">
         <v>241</v>
       </c>
-      <c r="C5" s="29" t="s">
+      <c r="C5" t="s">
         <v>242</v>
       </c>
       <c r="D5" t="s">
@@ -2484,10 +2525,10 @@
         <v>-20.93</v>
       </c>
       <c r="H5" t="n">
-        <v>0.003633489769</v>
-      </c>
-      <c r="I5" t="e">
-        <v>#N/A</v>
+        <v>0.0036</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.004</v>
       </c>
       <c r="J5" t="e">
         <v>#N/A</v>
@@ -2545,7 +2586,7 @@
       <c r="B6" t="s">
         <v>241</v>
       </c>
-      <c r="C6" s="29" t="s">
+      <c r="C6" t="s">
         <v>242</v>
       </c>
       <c r="D6" t="s">
@@ -2561,10 +2602,10 @@
         <v>-20.93</v>
       </c>
       <c r="H6" t="n">
-        <v>0.003633489769</v>
-      </c>
-      <c r="I6" t="e">
-        <v>#N/A</v>
+        <v>0.0036</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.004</v>
       </c>
       <c r="J6" t="e">
         <v>#N/A</v>
@@ -2622,7 +2663,7 @@
       <c r="B7" t="s">
         <v>241</v>
       </c>
-      <c r="C7" s="29" t="s">
+      <c r="C7" t="s">
         <v>242</v>
       </c>
       <c r="D7" t="s">
@@ -2638,10 +2679,10 @@
         <v>-20.93</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01460959912</v>
-      </c>
-      <c r="I7" t="e">
-        <v>#N/A</v>
+        <v>0.0146</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.004</v>
       </c>
       <c r="J7" t="e">
         <v>#N/A</v>
@@ -2699,7 +2740,7 @@
       <c r="B8" t="s">
         <v>241</v>
       </c>
-      <c r="C8" s="29" t="s">
+      <c r="C8" t="s">
         <v>242</v>
       </c>
       <c r="D8" t="s">
@@ -2715,10 +2756,10 @@
         <v>-20.93</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01460959912</v>
-      </c>
-      <c r="I8" t="e">
-        <v>#N/A</v>
+        <v>0.0146</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.004</v>
       </c>
       <c r="J8" t="e">
         <v>#N/A</v>
@@ -2776,7 +2817,7 @@
       <c r="B9" t="s">
         <v>241</v>
       </c>
-      <c r="C9" s="29" t="s">
+      <c r="C9" t="s">
         <v>242</v>
       </c>
       <c r="D9" t="s">
@@ -2792,10 +2833,10 @@
         <v>-20.93</v>
       </c>
       <c r="H9" t="n">
-        <v>0.02043604101</v>
-      </c>
-      <c r="I9" t="e">
-        <v>#N/A</v>
+        <v>0.0204</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.004</v>
       </c>
       <c r="J9" t="e">
         <v>#N/A</v>
@@ -2843,17 +2884,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y9" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1">
       <c r="A10" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B10" t="s">
         <v>241</v>
       </c>
-      <c r="C10" s="29" t="s">
+      <c r="C10" t="s">
         <v>242</v>
       </c>
       <c r="D10" t="s">
@@ -2869,10 +2910,10 @@
         <v>-20.93</v>
       </c>
       <c r="H10" t="n">
-        <v>0.04083738889</v>
-      </c>
-      <c r="I10" t="e">
-        <v>#N/A</v>
+        <v>0.0408</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.004</v>
       </c>
       <c r="J10" t="e">
         <v>#N/A</v>
@@ -2920,17 +2961,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y10" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
     </row>
     <row r="11" ht="19" customHeight="1">
       <c r="A11" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B11" t="s">
         <v>241</v>
       </c>
-      <c r="C11" s="29" t="s">
+      <c r="C11" t="s">
         <v>242</v>
       </c>
       <c r="D11" t="s">
@@ -2946,10 +2987,10 @@
         <v>-20.93</v>
       </c>
       <c r="H11" t="n">
-        <v>0.07057601416</v>
-      </c>
-      <c r="I11" t="e">
-        <v>#N/A</v>
+        <v>0.0706</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.004</v>
       </c>
       <c r="J11" t="e">
         <v>#N/A</v>
@@ -2997,17 +3038,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y11" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
     </row>
     <row r="12" ht="19" customHeight="1">
       <c r="A12" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="B12" t="s">
         <v>241</v>
       </c>
-      <c r="C12" s="29" t="s">
+      <c r="C12" t="s">
         <v>242</v>
       </c>
       <c r="D12" t="s">
@@ -3023,10 +3064,10 @@
         <v>-20.93</v>
       </c>
       <c r="H12" t="n">
-        <v>0.113572093</v>
-      </c>
-      <c r="I12" t="e">
-        <v>#N/A</v>
+        <v>0.1136</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.004</v>
       </c>
       <c r="J12" t="e">
         <v>#N/A</v>
@@ -3074,17 +3115,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y12" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
     </row>
     <row r="13" ht="19" customHeight="1">
       <c r="A13" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="B13" t="s">
         <v>241</v>
       </c>
-      <c r="C13" s="29" t="s">
+      <c r="C13" t="s">
         <v>242</v>
       </c>
       <c r="D13" t="s">
@@ -3100,10 +3141,10 @@
         <v>-20.93</v>
       </c>
       <c r="H13" t="n">
-        <v>0.1232337454</v>
-      </c>
-      <c r="I13" t="e">
-        <v>#N/A</v>
+        <v>0.1232</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.004</v>
       </c>
       <c r="J13" t="e">
         <v>#N/A</v>
@@ -3151,17 +3192,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y13" t="s">
-        <v>254</v>
+        <v>265</v>
       </c>
     </row>
     <row r="14" ht="19" customHeight="1">
       <c r="A14" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="B14" t="s">
         <v>241</v>
       </c>
-      <c r="C14" s="29" t="s">
+      <c r="C14" t="s">
         <v>242</v>
       </c>
       <c r="D14" t="s">
@@ -3177,10 +3218,10 @@
         <v>-20.93</v>
       </c>
       <c r="H14" t="n">
-        <v>0.128057612</v>
-      </c>
-      <c r="I14" t="e">
-        <v>#N/A</v>
+        <v>0.1281</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.004</v>
       </c>
       <c r="J14" t="e">
         <v>#N/A</v>
@@ -3228,17 +3269,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y14" t="s">
-        <v>254</v>
+        <v>267</v>
       </c>
     </row>
     <row r="15" ht="19" customHeight="1">
       <c r="A15" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="B15" t="s">
         <v>241</v>
       </c>
-      <c r="C15" s="29" t="s">
+      <c r="C15" t="s">
         <v>242</v>
       </c>
       <c r="D15" t="s">
@@ -3254,10 +3295,10 @@
         <v>-20.93</v>
       </c>
       <c r="H15" t="n">
-        <v>0.136837314</v>
-      </c>
-      <c r="I15" t="e">
-        <v>#N/A</v>
+        <v>0.1368</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.004</v>
       </c>
       <c r="J15" t="e">
         <v>#N/A</v>
@@ -3305,17 +3346,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y15" t="s">
-        <v>254</v>
+        <v>269</v>
       </c>
     </row>
     <row r="16" ht="19" customHeight="1">
       <c r="A16" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="B16" t="s">
         <v>241</v>
       </c>
-      <c r="C16" s="29" t="s">
+      <c r="C16" t="s">
         <v>242</v>
       </c>
       <c r="D16" t="s">
@@ -3331,10 +3372,10 @@
         <v>-20.93</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1385932544</v>
-      </c>
-      <c r="I16" t="e">
-        <v>#N/A</v>
+        <v>0.1386</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.004</v>
       </c>
       <c r="J16" t="e">
         <v>#N/A</v>
@@ -3382,17 +3423,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y16" t="s">
-        <v>254</v>
+        <v>271</v>
       </c>
     </row>
     <row r="17" ht="19" customHeight="1">
       <c r="A17" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="B17" t="s">
         <v>241</v>
       </c>
-      <c r="C17" s="29" t="s">
+      <c r="C17" t="s">
         <v>242</v>
       </c>
       <c r="D17" t="s">
@@ -3408,10 +3449,10 @@
         <v>-20.93</v>
       </c>
       <c r="H17" t="n">
-        <v>0.3291084577</v>
-      </c>
-      <c r="I17" t="e">
-        <v>#N/A</v>
+        <v>0.3291</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.004</v>
       </c>
       <c r="J17" t="e">
         <v>#N/A</v>
@@ -3459,17 +3500,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y17" t="s">
-        <v>254</v>
+        <v>273</v>
       </c>
     </row>
     <row r="18" ht="19" customHeight="1">
       <c r="A18" t="s">
-        <v>265</v>
+        <v>274</v>
       </c>
       <c r="B18" t="s">
         <v>241</v>
       </c>
-      <c r="C18" s="29" t="s">
+      <c r="C18" t="s">
         <v>242</v>
       </c>
       <c r="D18" t="s">
@@ -3485,10 +3526,10 @@
         <v>-20.93</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3585476801</v>
-      </c>
-      <c r="I18" t="e">
-        <v>#N/A</v>
+        <v>0.3585</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.004</v>
       </c>
       <c r="J18" t="e">
         <v>#N/A</v>
@@ -3536,17 +3577,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y18" t="s">
-        <v>254</v>
+        <v>275</v>
       </c>
     </row>
     <row r="19" ht="19" customHeight="1">
       <c r="A19" t="s">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="B19" t="s">
         <v>241</v>
       </c>
-      <c r="C19" s="29" t="s">
+      <c r="C19" t="s">
         <v>242</v>
       </c>
       <c r="D19" t="s">
@@ -3562,10 +3603,10 @@
         <v>-20.93</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3668924332</v>
-      </c>
-      <c r="I19" t="e">
-        <v>#N/A</v>
+        <v>0.3669</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.004</v>
       </c>
       <c r="J19" t="e">
         <v>#N/A</v>
@@ -3613,17 +3654,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y19" t="s">
-        <v>254</v>
+        <v>277</v>
       </c>
     </row>
     <row r="20" ht="19" customHeight="1">
       <c r="A20" t="s">
-        <v>267</v>
+        <v>278</v>
       </c>
       <c r="B20" t="s">
         <v>241</v>
       </c>
-      <c r="C20" s="29" t="s">
+      <c r="C20" t="s">
         <v>242</v>
       </c>
       <c r="D20" t="s">
@@ -3639,10 +3680,10 @@
         <v>-20.93</v>
       </c>
       <c r="H20" t="n">
-        <v>0.3863719272</v>
-      </c>
-      <c r="I20" t="e">
-        <v>#N/A</v>
+        <v>0.3864</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.004</v>
       </c>
       <c r="J20" t="e">
         <v>#N/A</v>
@@ -3690,17 +3731,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y20" t="s">
-        <v>254</v>
+        <v>279</v>
       </c>
     </row>
     <row r="21" ht="19" customHeight="1">
       <c r="A21" t="s">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="B21" t="s">
         <v>241</v>
       </c>
-      <c r="C21" s="29" t="s">
+      <c r="C21" t="s">
         <v>242</v>
       </c>
       <c r="D21" t="s">
@@ -3716,10 +3757,10 @@
         <v>-20.93</v>
       </c>
       <c r="H21" t="n">
-        <v>0.409091674</v>
-      </c>
-      <c r="I21" t="e">
-        <v>#N/A</v>
+        <v>0.4091</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.004</v>
       </c>
       <c r="J21" t="e">
         <v>#N/A</v>
@@ -3767,17 +3808,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y21" t="s">
-        <v>254</v>
+        <v>281</v>
       </c>
     </row>
     <row r="22" ht="19" customHeight="1">
       <c r="A22" t="s">
-        <v>269</v>
+        <v>282</v>
       </c>
       <c r="B22" t="s">
         <v>241</v>
       </c>
-      <c r="C22" s="29" t="s">
+      <c r="C22" t="s">
         <v>242</v>
       </c>
       <c r="D22" t="s">
@@ -3793,10 +3834,10 @@
         <v>-20.93</v>
       </c>
       <c r="H22" t="n">
-        <v>0.4188140124</v>
-      </c>
-      <c r="I22" t="e">
-        <v>#N/A</v>
+        <v>0.4188</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.004</v>
       </c>
       <c r="J22" t="e">
         <v>#N/A</v>
@@ -3844,17 +3885,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y22" t="s">
-        <v>254</v>
+        <v>283</v>
       </c>
     </row>
     <row r="23" ht="19" customHeight="1">
       <c r="A23" t="s">
-        <v>270</v>
+        <v>284</v>
       </c>
       <c r="B23" t="s">
         <v>241</v>
       </c>
-      <c r="C23" s="29" t="s">
+      <c r="C23" t="s">
         <v>242</v>
       </c>
       <c r="D23" t="s">
@@ -3870,10 +3911,10 @@
         <v>-20.93</v>
       </c>
       <c r="H23" t="n">
-        <v>0.5415533271</v>
-      </c>
-      <c r="I23" t="e">
-        <v>#N/A</v>
+        <v>0.5416</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.004</v>
       </c>
       <c r="J23" t="e">
         <v>#N/A</v>
@@ -3921,17 +3962,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y23" t="s">
-        <v>271</v>
+        <v>285</v>
       </c>
     </row>
     <row r="24" ht="19" customHeight="1">
       <c r="A24" t="s">
-        <v>272</v>
+        <v>286</v>
       </c>
       <c r="B24" t="s">
         <v>241</v>
       </c>
-      <c r="C24" s="29" t="s">
+      <c r="C24" t="s">
         <v>242</v>
       </c>
       <c r="D24" t="s">
@@ -3947,10 +3988,10 @@
         <v>-20.93</v>
       </c>
       <c r="H24" t="n">
-        <v>0.6162669419</v>
-      </c>
-      <c r="I24" t="e">
-        <v>#N/A</v>
+        <v>0.6163</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.004</v>
       </c>
       <c r="J24" t="e">
         <v>#N/A</v>
@@ -3998,17 +4039,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y24" t="s">
-        <v>271</v>
+        <v>287</v>
       </c>
     </row>
     <row r="25" ht="19" customHeight="1">
       <c r="A25" t="s">
-        <v>273</v>
+        <v>288</v>
       </c>
       <c r="B25" t="s">
         <v>241</v>
       </c>
-      <c r="C25" s="29" t="s">
+      <c r="C25" t="s">
         <v>242</v>
       </c>
       <c r="D25" t="s">
@@ -4024,10 +4065,10 @@
         <v>-20.93</v>
       </c>
       <c r="H25" t="n">
-        <v>0.6509888885</v>
-      </c>
-      <c r="I25" t="e">
-        <v>#N/A</v>
+        <v>0.651</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.004</v>
       </c>
       <c r="J25" t="e">
         <v>#N/A</v>
@@ -4045,7 +4086,7 @@
         <v>247</v>
       </c>
       <c r="O25" t="s">
-        <v>274</v>
+        <v>289</v>
       </c>
       <c r="P25" t="s">
         <v>249</v>
@@ -4075,17 +4116,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y25" t="s">
-        <v>271</v>
+        <v>287</v>
       </c>
     </row>
     <row r="26" ht="19" customHeight="1">
       <c r="A26" t="s">
-        <v>275</v>
+        <v>290</v>
       </c>
       <c r="B26" t="s">
         <v>241</v>
       </c>
-      <c r="C26" s="29" t="s">
+      <c r="C26" t="s">
         <v>242</v>
       </c>
       <c r="D26" t="s">
@@ -4101,10 +4142,10 @@
         <v>-20.93</v>
       </c>
       <c r="H26" t="n">
-        <v>0.6620787662</v>
-      </c>
-      <c r="I26" t="e">
-        <v>#N/A</v>
+        <v>0.6621</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.004</v>
       </c>
       <c r="J26" t="e">
         <v>#N/A</v>
@@ -4152,17 +4193,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y26" t="s">
-        <v>271</v>
+        <v>287</v>
       </c>
     </row>
     <row r="27" ht="19" customHeight="1">
       <c r="A27" t="s">
-        <v>276</v>
+        <v>291</v>
       </c>
       <c r="B27" t="s">
         <v>241</v>
       </c>
-      <c r="C27" s="29" t="s">
+      <c r="C27" t="s">
         <v>242</v>
       </c>
       <c r="D27" t="s">
@@ -4178,10 +4219,10 @@
         <v>-20.93</v>
       </c>
       <c r="H27" t="n">
-        <v>0.6750397195</v>
-      </c>
-      <c r="I27" t="e">
-        <v>#N/A</v>
+        <v>0.675</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.004</v>
       </c>
       <c r="J27" t="e">
         <v>#N/A</v>
@@ -4229,17 +4270,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y27" t="s">
-        <v>271</v>
+        <v>287</v>
       </c>
     </row>
     <row r="28" ht="19" customHeight="1">
       <c r="A28" t="s">
-        <v>277</v>
+        <v>292</v>
       </c>
       <c r="B28" t="s">
         <v>241</v>
       </c>
-      <c r="C28" s="29" t="s">
+      <c r="C28" t="s">
         <v>242</v>
       </c>
       <c r="D28" t="s">
@@ -4255,10 +4296,10 @@
         <v>-20.93</v>
       </c>
       <c r="H28" t="n">
-        <v>0.7021715786</v>
-      </c>
-      <c r="I28" t="e">
-        <v>#N/A</v>
+        <v>0.7022</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.004</v>
       </c>
       <c r="J28" t="e">
         <v>#N/A</v>
@@ -4306,17 +4347,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y28" t="s">
-        <v>271</v>
+        <v>287</v>
       </c>
     </row>
     <row r="29" ht="19" customHeight="1">
       <c r="A29" t="s">
-        <v>278</v>
+        <v>293</v>
       </c>
       <c r="B29" t="s">
         <v>241</v>
       </c>
-      <c r="C29" s="29" t="s">
+      <c r="C29" t="s">
         <v>242</v>
       </c>
       <c r="D29" t="s">
@@ -4332,10 +4373,10 @@
         <v>-20.93</v>
       </c>
       <c r="H29" t="n">
-        <v>0.7035076784</v>
-      </c>
-      <c r="I29" t="e">
-        <v>#N/A</v>
+        <v>0.7035</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.004</v>
       </c>
       <c r="J29" t="e">
         <v>#N/A</v>
@@ -4383,17 +4424,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y29" t="s">
-        <v>271</v>
+        <v>287</v>
       </c>
     </row>
     <row r="30" ht="19" customHeight="1">
       <c r="A30" t="s">
-        <v>279</v>
+        <v>294</v>
       </c>
       <c r="B30" t="s">
         <v>241</v>
       </c>
-      <c r="C30" s="29" t="s">
+      <c r="C30" t="s">
         <v>242</v>
       </c>
       <c r="D30" t="s">
@@ -4409,10 +4450,10 @@
         <v>-20.93</v>
       </c>
       <c r="H30" t="n">
-        <v>0.7310244511</v>
-      </c>
-      <c r="I30" t="e">
-        <v>#N/A</v>
+        <v>0.731</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.004</v>
       </c>
       <c r="J30" t="e">
         <v>#N/A</v>
@@ -4460,17 +4501,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y30" t="s">
-        <v>271</v>
+        <v>287</v>
       </c>
     </row>
     <row r="31" ht="19" customHeight="1">
       <c r="A31" t="s">
-        <v>280</v>
+        <v>295</v>
       </c>
       <c r="B31" t="s">
         <v>241</v>
       </c>
-      <c r="C31" s="29" t="s">
+      <c r="C31" t="s">
         <v>242</v>
       </c>
       <c r="D31" t="s">
@@ -4486,10 +4527,10 @@
         <v>-20.93</v>
       </c>
       <c r="H31" t="n">
-        <v>0.7524259159</v>
-      </c>
-      <c r="I31" t="e">
-        <v>#N/A</v>
+        <v>0.7524</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.004</v>
       </c>
       <c r="J31" t="e">
         <v>#N/A</v>
@@ -4537,17 +4578,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y31" t="s">
-        <v>271</v>
+        <v>287</v>
       </c>
     </row>
     <row r="32" ht="19" customHeight="1">
       <c r="A32" t="s">
-        <v>281</v>
+        <v>296</v>
       </c>
       <c r="B32" t="s">
         <v>241</v>
       </c>
-      <c r="C32" s="29" t="s">
+      <c r="C32" t="s">
         <v>242</v>
       </c>
       <c r="D32" t="s">
@@ -4563,10 +4604,10 @@
         <v>-20.93</v>
       </c>
       <c r="H32" t="n">
-        <v>0.8918939458</v>
-      </c>
-      <c r="I32" t="e">
-        <v>#N/A</v>
+        <v>0.8919</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.004</v>
       </c>
       <c r="J32" t="e">
         <v>#N/A</v>
@@ -4619,12 +4660,12 @@
     </row>
     <row r="33" ht="19" customHeight="1">
       <c r="A33" t="s">
-        <v>282</v>
+        <v>297</v>
       </c>
       <c r="B33" t="s">
         <v>241</v>
       </c>
-      <c r="C33" s="29" t="s">
+      <c r="C33" t="s">
         <v>242</v>
       </c>
       <c r="D33" t="s">
@@ -4640,10 +4681,10 @@
         <v>-20.93</v>
       </c>
       <c r="H33" t="n">
-        <v>0.9499855935</v>
-      </c>
-      <c r="I33" t="e">
-        <v>#N/A</v>
+        <v>0.95</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.004</v>
       </c>
       <c r="J33" t="e">
         <v>#N/A</v>
@@ -4661,7 +4702,7 @@
         <v>247</v>
       </c>
       <c r="O33" t="s">
-        <v>283</v>
+        <v>298</v>
       </c>
       <c r="P33" t="s">
         <v>249</v>
@@ -4696,12 +4737,12 @@
     </row>
     <row r="34" ht="19" customHeight="1">
       <c r="A34" t="s">
-        <v>284</v>
+        <v>299</v>
       </c>
       <c r="B34" t="s">
         <v>241</v>
       </c>
-      <c r="C34" s="29" t="s">
+      <c r="C34" t="s">
         <v>242</v>
       </c>
       <c r="D34" t="s">
@@ -4717,10 +4758,10 @@
         <v>-20.93</v>
       </c>
       <c r="H34" t="n">
-        <v>0.9528391112</v>
-      </c>
-      <c r="I34" t="e">
-        <v>#N/A</v>
+        <v>0.9528</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.004</v>
       </c>
       <c r="J34" t="e">
         <v>#N/A</v>
@@ -4773,12 +4814,12 @@
     </row>
     <row r="35" ht="19" customHeight="1">
       <c r="A35" t="s">
-        <v>285</v>
+        <v>300</v>
       </c>
       <c r="B35" t="s">
         <v>241</v>
       </c>
-      <c r="C35" s="29" t="s">
+      <c r="C35" t="s">
         <v>242</v>
       </c>
       <c r="D35" t="s">
@@ -4794,10 +4835,10 @@
         <v>-20.93</v>
       </c>
       <c r="H35" t="n">
-        <v>1.072816744</v>
-      </c>
-      <c r="I35" t="e">
-        <v>#N/A</v>
+        <v>1.0728</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.006</v>
       </c>
       <c r="J35" t="e">
         <v>#N/A</v>
@@ -4850,12 +4891,12 @@
     </row>
     <row r="36" ht="19" customHeight="1">
       <c r="A36" t="s">
-        <v>286</v>
+        <v>301</v>
       </c>
       <c r="B36" t="s">
         <v>241</v>
       </c>
-      <c r="C36" s="29" t="s">
+      <c r="C36" t="s">
         <v>242</v>
       </c>
       <c r="D36" t="s">
@@ -4871,10 +4912,10 @@
         <v>-20.93</v>
       </c>
       <c r="H36" t="n">
-        <v>1.078918302</v>
-      </c>
-      <c r="I36" t="e">
-        <v>#N/A</v>
+        <v>1.0789</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.006</v>
       </c>
       <c r="J36" t="e">
         <v>#N/A</v>
@@ -4927,12 +4968,12 @@
     </row>
     <row r="37" ht="19" customHeight="1">
       <c r="A37" t="s">
-        <v>287</v>
+        <v>302</v>
       </c>
       <c r="B37" t="s">
         <v>241</v>
       </c>
-      <c r="C37" s="29" t="s">
+      <c r="C37" t="s">
         <v>242</v>
       </c>
       <c r="D37" t="s">
@@ -4948,10 +4989,10 @@
         <v>-20.93</v>
       </c>
       <c r="H37" t="n">
-        <v>1.168280601</v>
-      </c>
-      <c r="I37" t="e">
-        <v>#N/A</v>
+        <v>1.1683</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.006</v>
       </c>
       <c r="J37" t="e">
         <v>#N/A</v>
@@ -4969,7 +5010,7 @@
         <v>247</v>
       </c>
       <c r="O37" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="P37" t="s">
         <v>249</v>
@@ -4999,17 +5040,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y37" t="s">
-        <v>271</v>
+        <v>287</v>
       </c>
     </row>
     <row r="38" ht="19" customHeight="1">
       <c r="A38" t="s">
-        <v>289</v>
+        <v>304</v>
       </c>
       <c r="B38" t="s">
         <v>241</v>
       </c>
-      <c r="C38" s="29" t="s">
+      <c r="C38" t="s">
         <v>242</v>
       </c>
       <c r="D38" t="s">
@@ -5025,10 +5066,10 @@
         <v>-20.93</v>
       </c>
       <c r="H38" t="n">
-        <v>1.19244841</v>
-      </c>
-      <c r="I38" t="e">
-        <v>#N/A</v>
+        <v>1.1924</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.006</v>
       </c>
       <c r="J38" t="e">
         <v>#N/A</v>
@@ -5076,17 +5117,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y38" t="s">
-        <v>271</v>
+        <v>287</v>
       </c>
     </row>
     <row r="39" ht="19" customHeight="1">
       <c r="A39" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="B39" t="s">
         <v>241</v>
       </c>
-      <c r="C39" s="29" t="s">
+      <c r="C39" t="s">
         <v>242</v>
       </c>
       <c r="D39" t="s">
@@ -5102,10 +5143,10 @@
         <v>-20.93</v>
       </c>
       <c r="H39" t="n">
-        <v>1.212548537</v>
-      </c>
-      <c r="I39" t="e">
-        <v>#N/A</v>
+        <v>1.2125</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.006</v>
       </c>
       <c r="J39" t="e">
         <v>#N/A</v>
@@ -5153,17 +5194,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y39" t="s">
-        <v>271</v>
+        <v>287</v>
       </c>
     </row>
     <row r="40" ht="19" customHeight="1">
       <c r="A40" t="s">
-        <v>291</v>
+        <v>306</v>
       </c>
       <c r="B40" t="s">
         <v>241</v>
       </c>
-      <c r="C40" s="29" t="s">
+      <c r="C40" t="s">
         <v>242</v>
       </c>
       <c r="D40" t="s">
@@ -5179,10 +5220,10 @@
         <v>-20.93</v>
       </c>
       <c r="H40" t="n">
-        <v>1.233289148</v>
-      </c>
-      <c r="I40" t="e">
-        <v>#N/A</v>
+        <v>1.2333</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.006</v>
       </c>
       <c r="J40" t="e">
         <v>#N/A</v>
@@ -5230,17 +5271,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y40" t="s">
-        <v>271</v>
+        <v>287</v>
       </c>
     </row>
     <row r="41" ht="19" customHeight="1">
       <c r="A41" t="s">
-        <v>292</v>
+        <v>307</v>
       </c>
       <c r="B41" t="s">
         <v>241</v>
       </c>
-      <c r="C41" s="29" t="s">
+      <c r="C41" t="s">
         <v>242</v>
       </c>
       <c r="D41" t="s">
@@ -5256,10 +5297,10 @@
         <v>-20.93</v>
       </c>
       <c r="H41" t="n">
-        <v>1.238673954</v>
-      </c>
-      <c r="I41" t="e">
-        <v>#N/A</v>
+        <v>1.2387</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.006</v>
       </c>
       <c r="J41" t="e">
         <v>#N/A</v>
@@ -5307,17 +5348,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y41" t="s">
-        <v>271</v>
+        <v>287</v>
       </c>
     </row>
     <row r="42" ht="19" customHeight="1">
       <c r="A42" t="s">
-        <v>293</v>
+        <v>308</v>
       </c>
       <c r="B42" t="s">
         <v>241</v>
       </c>
-      <c r="C42" s="29" t="s">
+      <c r="C42" t="s">
         <v>242</v>
       </c>
       <c r="D42" t="s">
@@ -5333,10 +5374,10 @@
         <v>-20.93</v>
       </c>
       <c r="H42" t="n">
-        <v>1.252997506</v>
-      </c>
-      <c r="I42" t="e">
-        <v>#N/A</v>
+        <v>1.253</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.006</v>
       </c>
       <c r="J42" t="e">
         <v>#N/A</v>
@@ -5384,17 +5425,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y42" t="s">
-        <v>271</v>
+        <v>287</v>
       </c>
     </row>
     <row r="43" ht="19" customHeight="1">
       <c r="A43" t="s">
-        <v>294</v>
+        <v>309</v>
       </c>
       <c r="B43" t="s">
         <v>241</v>
       </c>
-      <c r="C43" s="29" t="s">
+      <c r="C43" t="s">
         <v>242</v>
       </c>
       <c r="D43" t="s">
@@ -5410,10 +5451,10 @@
         <v>-20.93</v>
       </c>
       <c r="H43" t="n">
-        <v>1.261657928</v>
-      </c>
-      <c r="I43" t="e">
-        <v>#N/A</v>
+        <v>1.2617</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.006</v>
       </c>
       <c r="J43" t="e">
         <v>#N/A</v>
@@ -5461,17 +5502,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y43" t="s">
-        <v>271</v>
+        <v>287</v>
       </c>
     </row>
     <row r="44" ht="19" customHeight="1">
       <c r="A44" t="s">
-        <v>295</v>
+        <v>310</v>
       </c>
       <c r="B44" t="s">
         <v>241</v>
       </c>
-      <c r="C44" s="29" t="s">
+      <c r="C44" t="s">
         <v>242</v>
       </c>
       <c r="D44" t="s">
@@ -5487,10 +5528,10 @@
         <v>-20.93</v>
       </c>
       <c r="H44" t="n">
-        <v>1.353310353</v>
-      </c>
-      <c r="I44" t="e">
-        <v>#N/A</v>
+        <v>1.351571</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.006</v>
       </c>
       <c r="J44" t="e">
         <v>#N/A</v>
@@ -5498,8 +5539,8 @@
       <c r="K44" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L44" t="e">
-        <v>#N/A</v>
+      <c r="L44" t="s">
+        <v>311</v>
       </c>
       <c r="M44" t="s">
         <v>246</v>
@@ -5538,17 +5579,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y44" t="s">
-        <v>271</v>
+        <v>287</v>
       </c>
     </row>
     <row r="45" ht="19" customHeight="1">
       <c r="A45" t="s">
-        <v>296</v>
+        <v>312</v>
       </c>
       <c r="B45" t="s">
         <v>241</v>
       </c>
-      <c r="C45" s="29" t="s">
+      <c r="C45" t="s">
         <v>242</v>
       </c>
       <c r="D45" t="s">
@@ -5564,10 +5605,10 @@
         <v>-20.93</v>
       </c>
       <c r="H45" t="n">
-        <v>1.412700896</v>
-      </c>
-      <c r="I45" t="e">
-        <v>#N/A</v>
+        <v>1.380308</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.006</v>
       </c>
       <c r="J45" t="e">
         <v>#N/A</v>
@@ -5575,8 +5616,8 @@
       <c r="K45" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L45" t="e">
-        <v>#N/A</v>
+      <c r="L45" t="s">
+        <v>311</v>
       </c>
       <c r="M45" t="s">
         <v>246</v>
@@ -5615,17 +5656,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y45" t="s">
-        <v>271</v>
+        <v>287</v>
       </c>
     </row>
     <row r="46" ht="19" customHeight="1">
       <c r="A46" t="s">
-        <v>297</v>
+        <v>313</v>
       </c>
       <c r="B46" t="s">
         <v>241</v>
       </c>
-      <c r="C46" s="29" t="s">
+      <c r="C46" t="s">
         <v>242</v>
       </c>
       <c r="D46" t="s">
@@ -5641,10 +5682,10 @@
         <v>-20.93</v>
       </c>
       <c r="H46" t="n">
-        <v>1.4991555</v>
-      </c>
-      <c r="I46" t="e">
-        <v>#N/A</v>
+        <v>1.487</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0.006</v>
       </c>
       <c r="J46" t="e">
         <v>#N/A</v>
@@ -5652,8 +5693,8 @@
       <c r="K46" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L46" t="e">
-        <v>#N/A</v>
+      <c r="L46" t="s">
+        <v>311</v>
       </c>
       <c r="M46" t="s">
         <v>246</v>
@@ -5662,7 +5703,7 @@
         <v>247</v>
       </c>
       <c r="O46" t="s">
-        <v>298</v>
+        <v>314</v>
       </c>
       <c r="P46" t="s">
         <v>249</v>
@@ -5692,17 +5733,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y46" t="s">
-        <v>271</v>
+        <v>287</v>
       </c>
     </row>
     <row r="47" ht="19" customHeight="1">
       <c r="A47" t="s">
-        <v>299</v>
+        <v>315</v>
       </c>
       <c r="B47" t="s">
         <v>241</v>
       </c>
-      <c r="C47" s="29" t="s">
+      <c r="C47" t="s">
         <v>242</v>
       </c>
       <c r="D47" t="s">
@@ -5718,10 +5759,10 @@
         <v>-20.93</v>
       </c>
       <c r="H47" t="n">
-        <v>1.578882673</v>
-      </c>
-      <c r="I47" t="e">
-        <v>#N/A</v>
+        <v>1.499</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0.006</v>
       </c>
       <c r="J47" t="e">
         <v>#N/A</v>
@@ -5729,8 +5770,8 @@
       <c r="K47" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L47" t="e">
-        <v>#N/A</v>
+      <c r="L47" t="s">
+        <v>311</v>
       </c>
       <c r="M47" t="s">
         <v>246</v>
@@ -5769,17 +5810,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y47" t="s">
-        <v>271</v>
+        <v>287</v>
       </c>
     </row>
     <row r="48" ht="19" customHeight="1">
       <c r="A48" t="s">
-        <v>300</v>
+        <v>316</v>
       </c>
       <c r="B48" t="s">
         <v>241</v>
       </c>
-      <c r="C48" s="29" t="s">
+      <c r="C48" t="s">
         <v>242</v>
       </c>
       <c r="D48" t="s">
@@ -5795,10 +5836,10 @@
         <v>-20.93</v>
       </c>
       <c r="H48" t="n">
-        <v>1.653010236</v>
-      </c>
-      <c r="I48" t="e">
-        <v>#N/A</v>
+        <v>1.539</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0.006</v>
       </c>
       <c r="J48" t="e">
         <v>#N/A</v>
@@ -5806,8 +5847,8 @@
       <c r="K48" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L48" t="e">
-        <v>#N/A</v>
+      <c r="L48" t="s">
+        <v>311</v>
       </c>
       <c r="M48" t="s">
         <v>246</v>
@@ -5846,17 +5887,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y48" t="s">
-        <v>271</v>
+        <v>287</v>
       </c>
     </row>
     <row r="49" ht="19" customHeight="1">
       <c r="A49" t="s">
-        <v>301</v>
+        <v>317</v>
       </c>
       <c r="B49" t="s">
         <v>241</v>
       </c>
-      <c r="C49" s="29" t="s">
+      <c r="C49" t="s">
         <v>242</v>
       </c>
       <c r="D49" t="s">
@@ -5872,10 +5913,10 @@
         <v>-20.93</v>
       </c>
       <c r="H49" t="n">
-        <v>1.666789992</v>
-      </c>
-      <c r="I49" t="e">
-        <v>#N/A</v>
+        <v>1.5413</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0.006</v>
       </c>
       <c r="J49" t="e">
         <v>#N/A</v>
@@ -5883,8 +5924,8 @@
       <c r="K49" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L49" t="e">
-        <v>#N/A</v>
+      <c r="L49" t="s">
+        <v>311</v>
       </c>
       <c r="M49" t="s">
         <v>246</v>
@@ -5928,12 +5969,12 @@
     </row>
     <row r="50" ht="19" customHeight="1">
       <c r="A50" t="s">
-        <v>302</v>
+        <v>318</v>
       </c>
       <c r="B50" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="29" t="s">
+      <c r="C50" t="s">
         <v>242</v>
       </c>
       <c r="D50" t="s">
@@ -5949,10 +5990,10 @@
         <v>-20.93</v>
       </c>
       <c r="H50" t="n">
-        <v>1.673687301</v>
-      </c>
-      <c r="I50" t="e">
-        <v>#N/A</v>
+        <v>1.5423</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0.006</v>
       </c>
       <c r="J50" t="e">
         <v>#N/A</v>
@@ -5960,8 +6001,8 @@
       <c r="K50" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L50" t="e">
-        <v>#N/A</v>
+      <c r="L50" t="s">
+        <v>311</v>
       </c>
       <c r="M50" t="s">
         <v>246</v>
@@ -6000,17 +6041,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y50" t="s">
-        <v>271</v>
+        <v>287</v>
       </c>
     </row>
     <row r="51" ht="19" customHeight="1">
       <c r="A51" t="s">
-        <v>303</v>
+        <v>319</v>
       </c>
       <c r="B51" t="s">
         <v>241</v>
       </c>
-      <c r="C51" s="29" t="s">
+      <c r="C51" t="s">
         <v>242</v>
       </c>
       <c r="D51" t="s">
@@ -6026,10 +6067,10 @@
         <v>-20.93</v>
       </c>
       <c r="H51" t="n">
-        <v>1.854154015</v>
-      </c>
-      <c r="I51" t="e">
-        <v>#N/A</v>
+        <v>1.5741</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0.006</v>
       </c>
       <c r="J51" t="e">
         <v>#N/A</v>
@@ -6037,8 +6078,8 @@
       <c r="K51" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L51" t="e">
-        <v>#N/A</v>
+      <c r="L51" t="s">
+        <v>311</v>
       </c>
       <c r="M51" t="s">
         <v>246</v>
@@ -6082,12 +6123,12 @@
     </row>
     <row r="52" ht="19" customHeight="1">
       <c r="A52" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="B52" t="s">
         <v>241</v>
       </c>
-      <c r="C52" s="29" t="s">
+      <c r="C52" t="s">
         <v>242</v>
       </c>
       <c r="D52" t="s">
@@ -6103,10 +6144,10 @@
         <v>-20.93</v>
       </c>
       <c r="H52" t="n">
-        <v>1.863783488</v>
-      </c>
-      <c r="I52" t="e">
-        <v>#N/A</v>
+        <v>1.5774</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0.006</v>
       </c>
       <c r="J52" t="e">
         <v>#N/A</v>
@@ -6114,8 +6155,8 @@
       <c r="K52" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L52" t="e">
-        <v>#N/A</v>
+      <c r="L52" t="s">
+        <v>311</v>
       </c>
       <c r="M52" t="s">
         <v>246</v>
@@ -6159,12 +6200,12 @@
     </row>
     <row r="53" ht="19" customHeight="1">
       <c r="A53" t="s">
-        <v>305</v>
+        <v>321</v>
       </c>
       <c r="B53" t="s">
         <v>241</v>
       </c>
-      <c r="C53" s="29" t="s">
+      <c r="C53" t="s">
         <v>242</v>
       </c>
       <c r="D53" t="s">
@@ -6180,10 +6221,10 @@
         <v>-20.93</v>
       </c>
       <c r="H53" t="n">
-        <v>1.931754155</v>
-      </c>
-      <c r="I53" t="e">
-        <v>#N/A</v>
+        <v>1.616</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0.006</v>
       </c>
       <c r="J53" t="e">
         <v>#N/A</v>
@@ -6191,8 +6232,8 @@
       <c r="K53" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L53" t="e">
-        <v>#N/A</v>
+      <c r="L53" t="s">
+        <v>311</v>
       </c>
       <c r="M53" t="s">
         <v>246</v>
@@ -6231,17 +6272,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y53" t="s">
-        <v>271</v>
+        <v>287</v>
       </c>
     </row>
     <row r="54" ht="19" customHeight="1">
       <c r="A54" t="s">
-        <v>306</v>
+        <v>322</v>
       </c>
       <c r="B54" t="s">
         <v>241</v>
       </c>
-      <c r="C54" s="29" t="s">
+      <c r="C54" t="s">
         <v>242</v>
       </c>
       <c r="D54" t="s">
@@ -6257,10 +6298,10 @@
         <v>-20.93</v>
       </c>
       <c r="H54" t="n">
-        <v>1.94634205</v>
-      </c>
-      <c r="I54" t="e">
-        <v>#N/A</v>
+        <v>1.6446</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0.006</v>
       </c>
       <c r="J54" t="e">
         <v>#N/A</v>
@@ -6268,8 +6309,8 @@
       <c r="K54" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L54" t="e">
-        <v>#N/A</v>
+      <c r="L54" t="s">
+        <v>311</v>
       </c>
       <c r="M54" t="s">
         <v>246</v>
@@ -6278,7 +6319,7 @@
         <v>247</v>
       </c>
       <c r="O54" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
       <c r="P54" t="s">
         <v>249</v>
@@ -6308,17 +6349,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y54" t="s">
-        <v>307</v>
+        <v>323</v>
       </c>
     </row>
     <row r="55" ht="19" customHeight="1">
       <c r="A55" t="s">
-        <v>308</v>
+        <v>324</v>
       </c>
       <c r="B55" t="s">
         <v>241</v>
       </c>
-      <c r="C55" s="29" t="s">
+      <c r="C55" t="s">
         <v>242</v>
       </c>
       <c r="D55" t="s">
@@ -6334,10 +6375,10 @@
         <v>-20.93</v>
       </c>
       <c r="H55" t="n">
-        <v>1.948173226</v>
-      </c>
-      <c r="I55" t="e">
-        <v>#N/A</v>
+        <v>1.6487</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0.006</v>
       </c>
       <c r="J55" t="e">
         <v>#N/A</v>
@@ -6345,8 +6386,8 @@
       <c r="K55" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L55" t="e">
-        <v>#N/A</v>
+      <c r="L55" t="s">
+        <v>311</v>
       </c>
       <c r="M55" t="s">
         <v>246</v>
@@ -6355,7 +6396,7 @@
         <v>247</v>
       </c>
       <c r="O55" t="s">
-        <v>309</v>
+        <v>325</v>
       </c>
       <c r="P55" t="s">
         <v>249</v>
@@ -6390,12 +6431,12 @@
     </row>
     <row r="56" ht="19" customHeight="1">
       <c r="A56" t="s">
-        <v>310</v>
+        <v>326</v>
       </c>
       <c r="B56" t="s">
         <v>241</v>
       </c>
-      <c r="C56" s="29" t="s">
+      <c r="C56" t="s">
         <v>242</v>
       </c>
       <c r="D56" t="s">
@@ -6411,10 +6452,10 @@
         <v>-20.93</v>
       </c>
       <c r="H56" t="n">
-        <v>1.955829769</v>
-      </c>
-      <c r="I56" t="e">
-        <v>#N/A</v>
+        <v>1.6595</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0.006</v>
       </c>
       <c r="J56" t="e">
         <v>#N/A</v>
@@ -6422,8 +6463,8 @@
       <c r="K56" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L56" t="e">
-        <v>#N/A</v>
+      <c r="L56" t="s">
+        <v>311</v>
       </c>
       <c r="M56" t="s">
         <v>246</v>
@@ -6467,12 +6508,12 @@
     </row>
     <row r="57" ht="19" customHeight="1">
       <c r="A57" t="s">
-        <v>311</v>
+        <v>327</v>
       </c>
       <c r="B57" t="s">
         <v>241</v>
       </c>
-      <c r="C57" s="29" t="s">
+      <c r="C57" t="s">
         <v>242</v>
       </c>
       <c r="D57" t="s">
@@ -6488,10 +6529,10 @@
         <v>-20.93</v>
       </c>
       <c r="H57" t="n">
-        <v>1.979302676</v>
-      </c>
-      <c r="I57" t="e">
-        <v>#N/A</v>
+        <v>1.6985</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0.006</v>
       </c>
       <c r="J57" t="e">
         <v>#N/A</v>
@@ -6499,8 +6540,8 @@
       <c r="K57" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L57" t="e">
-        <v>#N/A</v>
+      <c r="L57" t="s">
+        <v>311</v>
       </c>
       <c r="M57" t="s">
         <v>246</v>
@@ -6544,12 +6585,12 @@
     </row>
     <row r="58" ht="19" customHeight="1">
       <c r="A58" t="s">
-        <v>312</v>
+        <v>328</v>
       </c>
       <c r="B58" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="29" t="s">
+      <c r="C58" t="s">
         <v>242</v>
       </c>
       <c r="D58" t="s">
@@ -6565,10 +6606,10 @@
         <v>-20.93</v>
       </c>
       <c r="H58" t="n">
-        <v>2.019731325</v>
-      </c>
-      <c r="I58" t="e">
-        <v>#N/A</v>
+        <v>1.7531</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0.006</v>
       </c>
       <c r="J58" t="e">
         <v>#N/A</v>
@@ -6576,8 +6617,8 @@
       <c r="K58" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L58" t="e">
-        <v>#N/A</v>
+      <c r="L58" t="s">
+        <v>311</v>
       </c>
       <c r="M58" t="s">
         <v>246</v>
@@ -6621,12 +6662,12 @@
     </row>
     <row r="59" ht="19" customHeight="1">
       <c r="A59" t="s">
-        <v>313</v>
+        <v>329</v>
       </c>
       <c r="B59" t="s">
         <v>241</v>
       </c>
-      <c r="C59" s="29" t="s">
+      <c r="C59" t="s">
         <v>242</v>
       </c>
       <c r="D59" t="s">
@@ -6642,10 +6683,10 @@
         <v>-20.93</v>
       </c>
       <c r="H59" t="n">
-        <v>2.042227782</v>
-      </c>
-      <c r="I59" t="e">
-        <v>#N/A</v>
+        <v>1.7749</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0.006</v>
       </c>
       <c r="J59" t="e">
         <v>#N/A</v>
@@ -6653,8 +6694,8 @@
       <c r="K59" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L59" t="e">
-        <v>#N/A</v>
+      <c r="L59" t="s">
+        <v>311</v>
       </c>
       <c r="M59" t="s">
         <v>246</v>
@@ -6663,7 +6704,7 @@
         <v>247</v>
       </c>
       <c r="O59" t="s">
-        <v>314</v>
+        <v>330</v>
       </c>
       <c r="P59" t="s">
         <v>249</v>
@@ -6693,17 +6734,17 @@
         <v>#N/A</v>
       </c>
       <c r="Y59" t="s">
-        <v>307</v>
+        <v>323</v>
       </c>
     </row>
     <row r="60" ht="19" customHeight="1">
       <c r="A60" t="s">
-        <v>315</v>
+        <v>331</v>
       </c>
       <c r="B60" t="s">
         <v>241</v>
       </c>
-      <c r="C60" s="29" t="s">
+      <c r="C60" t="s">
         <v>242</v>
       </c>
       <c r="D60" t="s">
@@ -6719,10 +6760,10 @@
         <v>-20.93</v>
       </c>
       <c r="H60" t="n">
-        <v>2.048189944</v>
-      </c>
-      <c r="I60" t="e">
-        <v>#N/A</v>
+        <v>1.7796</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0.006</v>
       </c>
       <c r="J60" t="e">
         <v>#N/A</v>
@@ -6730,8 +6771,8 @@
       <c r="K60" t="e">
         <v>#N/A</v>
       </c>
-      <c r="L60" t="e">
-        <v>#N/A</v>
+      <c r="L60" t="s">
+        <v>311</v>
       </c>
       <c r="M60" t="s">
         <v>246</v>
@@ -6740,7 +6781,7 @@
         <v>247</v>
       </c>
       <c r="O60" t="s">
-        <v>316</v>
+        <v>332</v>
       </c>
       <c r="P60" t="s">
         <v>249</v>
@@ -6917,64 +6958,6 @@
       <formula>#REF!="no"</formula>
     </cfRule>
   </conditionalFormatting>
-  <hyperlinks>
-    <hyperlink ref="C5" r:id="rId1h"/>
-    <hyperlink ref="C6" r:id="rId2h"/>
-    <hyperlink ref="C7" r:id="rId3h"/>
-    <hyperlink ref="C8" r:id="rId4h"/>
-    <hyperlink ref="C9" r:id="rId5h"/>
-    <hyperlink ref="C10" r:id="rId6h"/>
-    <hyperlink ref="C11" r:id="rId7h"/>
-    <hyperlink ref="C12" r:id="rId8h"/>
-    <hyperlink ref="C13" r:id="rId9h"/>
-    <hyperlink ref="C14" r:id="rId10h"/>
-    <hyperlink ref="C15" r:id="rId11h"/>
-    <hyperlink ref="C16" r:id="rId12h"/>
-    <hyperlink ref="C17" r:id="rId13h"/>
-    <hyperlink ref="C18" r:id="rId14h"/>
-    <hyperlink ref="C19" r:id="rId15h"/>
-    <hyperlink ref="C20" r:id="rId16h"/>
-    <hyperlink ref="C21" r:id="rId17h"/>
-    <hyperlink ref="C22" r:id="rId18h"/>
-    <hyperlink ref="C23" r:id="rId19h"/>
-    <hyperlink ref="C24" r:id="rId20h"/>
-    <hyperlink ref="C25" r:id="rId21h"/>
-    <hyperlink ref="C26" r:id="rId22h"/>
-    <hyperlink ref="C27" r:id="rId23h"/>
-    <hyperlink ref="C28" r:id="rId24h"/>
-    <hyperlink ref="C29" r:id="rId25h"/>
-    <hyperlink ref="C30" r:id="rId26h"/>
-    <hyperlink ref="C31" r:id="rId27h"/>
-    <hyperlink ref="C32" r:id="rId28h"/>
-    <hyperlink ref="C33" r:id="rId29h"/>
-    <hyperlink ref="C34" r:id="rId30h"/>
-    <hyperlink ref="C35" r:id="rId31h"/>
-    <hyperlink ref="C36" r:id="rId32h"/>
-    <hyperlink ref="C37" r:id="rId33h"/>
-    <hyperlink ref="C38" r:id="rId34h"/>
-    <hyperlink ref="C39" r:id="rId35h"/>
-    <hyperlink ref="C40" r:id="rId36h"/>
-    <hyperlink ref="C41" r:id="rId37h"/>
-    <hyperlink ref="C42" r:id="rId38h"/>
-    <hyperlink ref="C43" r:id="rId39h"/>
-    <hyperlink ref="C44" r:id="rId40h"/>
-    <hyperlink ref="C45" r:id="rId41h"/>
-    <hyperlink ref="C46" r:id="rId42h"/>
-    <hyperlink ref="C47" r:id="rId43h"/>
-    <hyperlink ref="C48" r:id="rId44h"/>
-    <hyperlink ref="C49" r:id="rId45h"/>
-    <hyperlink ref="C50" r:id="rId46h"/>
-    <hyperlink ref="C51" r:id="rId47h"/>
-    <hyperlink ref="C52" r:id="rId48h"/>
-    <hyperlink ref="C53" r:id="rId49h"/>
-    <hyperlink ref="C54" r:id="rId50h"/>
-    <hyperlink ref="C55" r:id="rId51h"/>
-    <hyperlink ref="C56" r:id="rId52h"/>
-    <hyperlink ref="C57" r:id="rId53h"/>
-    <hyperlink ref="C58" r:id="rId54h"/>
-    <hyperlink ref="C59" r:id="rId55h"/>
-    <hyperlink ref="C60" r:id="rId56h"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
   <extLst>
